--- a/Code/Youtube Data/video_ids.xlsx
+++ b/Code/Youtube Data/video_ids.xlsx
@@ -8,1063 +8,2403 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rusha\RD Documents\Rushabh's career\Computer Science\University\Year\Year 3\Semester 1\Web and Cloud Based Security\COMP-3226-Web-and-Cloud-Based-Security-\Code\Youtube Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3B6BEB9-8A6F-412D-A533-16233CFF08D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F915A052-D8FA-4B66-93F9-FCBAD3E448EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34485" yWindow="4740" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1836" yWindow="3456" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="795">
   <si>
     <t>videoID</t>
   </si>
   <si>
+    <t>KT18KJouHWg</t>
+  </si>
+  <si>
+    <t>FUHkTs-Ipfg</t>
+  </si>
+  <si>
+    <t>pTn6Ewhb27k</t>
+  </si>
+  <si>
+    <t>bHIhgxav9LY</t>
+  </si>
+  <si>
+    <t>oI_X2cMHNe0</t>
+  </si>
+  <si>
+    <t>j5v8D-alAKE</t>
+  </si>
+  <si>
+    <t>zB_OApdxcno</t>
+  </si>
+  <si>
+    <t>ZQ--scjcAZ4</t>
+  </si>
+  <si>
+    <t>XeSu9fBJ2sI</t>
+  </si>
+  <si>
+    <t>czjisEGe5Cw</t>
+  </si>
+  <si>
+    <t>vjDYfvPW4mA</t>
+  </si>
+  <si>
+    <t>yjztvddhZmI</t>
+  </si>
+  <si>
+    <t>zTDFhWWPZ4Q</t>
+  </si>
+  <si>
+    <t>fHsa9DqmId8</t>
+  </si>
+  <si>
+    <t>myh94hpFmJY</t>
+  </si>
+  <si>
+    <t>9zso7ChaQXQ</t>
+  </si>
+  <si>
+    <t>liqF6EamiE4</t>
+  </si>
+  <si>
+    <t>Ux33-5k8cjg</t>
+  </si>
+  <si>
+    <t>lL2e0rWvjKI</t>
+  </si>
+  <si>
+    <t>vqDbMEdLiCs</t>
+  </si>
+  <si>
+    <t>TQxeutcYP6I</t>
+  </si>
+  <si>
+    <t>2KZb2_vcNTg</t>
+  </si>
+  <si>
+    <t>Bz9D6xba9Og</t>
+  </si>
+  <si>
+    <t>esQyYGezS7c</t>
+  </si>
+  <si>
+    <t>QQkmJI63ykI</t>
+  </si>
+  <si>
+    <t>24GfgNtnjXc</t>
+  </si>
+  <si>
+    <t>_cr46G2K5Fo</t>
+  </si>
+  <si>
+    <t>SC2eSujzrUY</t>
+  </si>
+  <si>
+    <t>J3i3F2e4IYs</t>
+  </si>
+  <si>
+    <t>NIk_0AW5hFU</t>
+  </si>
+  <si>
+    <t>ZMQbHMgK2rw</t>
+  </si>
+  <si>
+    <t>eLVAMG_3fLg</t>
+  </si>
+  <si>
+    <t>daaDuC1kbds</t>
+  </si>
+  <si>
+    <t>vSNtifE0Z2Q</t>
+  </si>
+  <si>
+    <t>vS0TuIPoeBs</t>
+  </si>
+  <si>
+    <t>UAeJHAFjwPM</t>
+  </si>
+  <si>
+    <t>w5ebcowAJD8</t>
+  </si>
+  <si>
+    <t>lfkjm2YRG-Q</t>
+  </si>
+  <si>
+    <t>ZjBgEkbnX2I</t>
+  </si>
+  <si>
+    <t>V9K6gjR07Po</t>
+  </si>
+  <si>
+    <t>nGxr8-l0vHI</t>
+  </si>
+  <si>
+    <t>zPbrkmdcTfo</t>
+  </si>
+  <si>
+    <t>YJOmxjtG9IM</t>
+  </si>
+  <si>
+    <t>QS87RLjFE_g</t>
+  </si>
+  <si>
+    <t>rCjJItWMxqI</t>
+  </si>
+  <si>
+    <t>bTCQhMMfse0</t>
+  </si>
+  <si>
+    <t>9bLD0tVep9M</t>
+  </si>
+  <si>
+    <t>PWirijQkH4M</t>
+  </si>
+  <si>
+    <t>nIjVuRTm-dc</t>
+  </si>
+  <si>
+    <t>V9vuCByb6js</t>
+  </si>
+  <si>
+    <t>CYobbeiGgp8</t>
+  </si>
+  <si>
+    <t>cJipa07DoHs</t>
+  </si>
+  <si>
+    <t>sv71JMZEpYY</t>
+  </si>
+  <si>
+    <t>_2K2CbC7ppA</t>
+  </si>
+  <si>
+    <t>wjWMOYLNK_E</t>
+  </si>
+  <si>
+    <t>k6ZoE4RrcDs</t>
+  </si>
+  <si>
+    <t>d9h_qtOoFnA</t>
+  </si>
+  <si>
+    <t>fMsolCIjr5k</t>
+  </si>
+  <si>
+    <t>yQN4LqcLAgA</t>
+  </si>
+  <si>
+    <t>Bi0taCrL22Q</t>
+  </si>
+  <si>
+    <t>wXFQ-ibAIIM</t>
+  </si>
+  <si>
+    <t>8DkcTriimSM</t>
+  </si>
+  <si>
+    <t>MiiNi4cfP4U</t>
+  </si>
+  <si>
+    <t>mml5N4kA4ZY</t>
+  </si>
+  <si>
+    <t>YpUgnlZkPEI</t>
+  </si>
+  <si>
+    <t>Tsqw78IgEmA</t>
+  </si>
+  <si>
+    <t>SJVMdDgPJZU</t>
+  </si>
+  <si>
+    <t>mDnQnoNhez0</t>
+  </si>
+  <si>
+    <t>cimoNqiulUE</t>
+  </si>
+  <si>
+    <t>JyOYBJmhZ2Q</t>
+  </si>
+  <si>
+    <t>ZauGjgZ0rBQ</t>
+  </si>
+  <si>
+    <t>qTjA2L3j5Po</t>
+  </si>
+  <si>
+    <t>248Kjm9UMtg</t>
+  </si>
+  <si>
+    <t>FseDdBrkhK4</t>
+  </si>
+  <si>
+    <t>jObOjhUkf50</t>
+  </si>
+  <si>
+    <t>TtgUzJsXq6U</t>
+  </si>
+  <si>
+    <t>BadBueh22qs</t>
+  </si>
+  <si>
+    <t>moSE2_ur994</t>
+  </si>
+  <si>
+    <t>57C13H0BnnU</t>
+  </si>
+  <si>
+    <t>a3w3C6ATGrY</t>
+  </si>
+  <si>
+    <t>inlj61TsIRw</t>
+  </si>
+  <si>
+    <t>xDi_TTbk3-c</t>
+  </si>
+  <si>
+    <t>Bd2fE3YO7Aw</t>
+  </si>
+  <si>
+    <t>omCQKtI6OFM</t>
+  </si>
+  <si>
+    <t>wURhR2Vtm8E</t>
+  </si>
+  <si>
+    <t>rPql1XEqa5Q</t>
+  </si>
+  <si>
+    <t>txk--OgckSQ</t>
+  </si>
+  <si>
+    <t>XGFnZ-xGHsg</t>
+  </si>
+  <si>
+    <t>TJ2ifmkGGus</t>
+  </si>
+  <si>
+    <t>7dYTw-jAYkY</t>
+  </si>
+  <si>
+    <t>09JYAZEoOOk</t>
+  </si>
+  <si>
+    <t>tivtBueDg_c</t>
+  </si>
+  <si>
+    <t>zGLUqrUMWK0</t>
+  </si>
+  <si>
+    <t>b4fx6BjWEqk</t>
+  </si>
+  <si>
+    <t>uK6RaiZdzCo</t>
+  </si>
+  <si>
+    <t>Dqeg_rH8VAI</t>
+  </si>
+  <si>
+    <t>vO4QeHR9SXM</t>
+  </si>
+  <si>
+    <t>PaFMAgfkpyY</t>
+  </si>
+  <si>
+    <t>noJCNh60lfk</t>
+  </si>
+  <si>
+    <t>pDddlvCfTiw</t>
+  </si>
+  <si>
+    <t>4SNThp0YiU4</t>
+  </si>
+  <si>
+    <t>MbJ72KO5khs</t>
+  </si>
+  <si>
+    <t>sJj3q6njVbM</t>
+  </si>
+  <si>
+    <t>PCpvt3wk42A</t>
+  </si>
+  <si>
+    <t>4DgTtRIvPvE</t>
+  </si>
+  <si>
+    <t>sxjC4CNG3_c</t>
+  </si>
+  <si>
+    <t>_Y2smOELBxk</t>
+  </si>
+  <si>
+    <t>QHorNUuEXc0</t>
+  </si>
+  <si>
+    <t>HHuTrcXNxOk</t>
+  </si>
+  <si>
+    <t>pZ2lBWBCEnU</t>
+  </si>
+  <si>
+    <t>DHR6usutswA</t>
+  </si>
+  <si>
+    <t>SM66GDRyIVY</t>
+  </si>
+  <si>
+    <t>wYZux3BMc5k</t>
+  </si>
+  <si>
+    <t>klHr7F_xIig</t>
+  </si>
+  <si>
+    <t>Z-062PWH0vo</t>
+  </si>
+  <si>
+    <t>fIcWfHikAOo</t>
+  </si>
+  <si>
+    <t>_P7wHN_kOv4</t>
+  </si>
+  <si>
+    <t>kaqxOKmq0ZI</t>
+  </si>
+  <si>
+    <t>PR0gwyZYZ_Q</t>
+  </si>
+  <si>
+    <t>9-llcas2hOE</t>
+  </si>
+  <si>
+    <t>uzKtZwY_xqw</t>
+  </si>
+  <si>
+    <t>XbGs_qK2PQA</t>
+  </si>
+  <si>
+    <t>Aan-kc-9E3A</t>
+  </si>
+  <si>
+    <t>xhIFmxslJCQ</t>
+  </si>
+  <si>
+    <t>YSrjyXqA5cM</t>
+  </si>
+  <si>
+    <t>9RhWXPcKBI8</t>
+  </si>
+  <si>
+    <t>UPOT2tgY9QQ</t>
+  </si>
+  <si>
+    <t>zz5lGkDdk78</t>
+  </si>
+  <si>
+    <t>h_kGwBANynQ</t>
+  </si>
+  <si>
+    <t>pMRxeZAKWvk</t>
+  </si>
+  <si>
+    <t>mcTpep5uoZ8</t>
+  </si>
+  <si>
+    <t>rlNvpQRlSHA</t>
+  </si>
+  <si>
+    <t>moTRUU4MRPM</t>
+  </si>
+  <si>
+    <t>myjEoDypUD8</t>
+  </si>
+  <si>
+    <t>zRzR0So7Ans</t>
+  </si>
+  <si>
+    <t>di_DaFQSw1c</t>
+  </si>
+  <si>
+    <t>A3cfB5fDN1E</t>
+  </si>
+  <si>
+    <t>KvLGDbU6PIk</t>
+  </si>
+  <si>
+    <t>kKr1XiGryF4</t>
+  </si>
+  <si>
+    <t>73tpsJeIsHU</t>
+  </si>
+  <si>
+    <t>muT3_bTXR_w</t>
+  </si>
+  <si>
+    <t>mKEphyIbtXo</t>
+  </si>
+  <si>
+    <t>2S7HEwRLyew</t>
+  </si>
+  <si>
+    <t>V_jHc_n0p9c</t>
+  </si>
+  <si>
+    <t>8oRj4wvomzs</t>
+  </si>
+  <si>
+    <t>PjZvJZ6wRe8</t>
+  </si>
+  <si>
+    <t>wON9BvL_Lyw</t>
+  </si>
+  <si>
+    <t>eGUor824a74</t>
+  </si>
+  <si>
+    <t>YqKYpgZ9FWU</t>
+  </si>
+  <si>
+    <t>Mh5dKiiZRlg</t>
+  </si>
+  <si>
+    <t>zAd6mDrJz-8</t>
+  </si>
+  <si>
+    <t>JvbfRPAcN2A</t>
+  </si>
+  <si>
+    <t>xqYb1hMQKV4</t>
+  </si>
+  <si>
+    <t>OHkRYXwD87A</t>
+  </si>
+  <si>
+    <t>BrA_pb9rCJE</t>
+  </si>
+  <si>
+    <t>jgliCvYQ4hY</t>
+  </si>
+  <si>
+    <t>biyH0s6tbAU</t>
+  </si>
+  <si>
+    <t>kkWE459slL8</t>
+  </si>
+  <si>
+    <t>AK3HbkbgiQA</t>
+  </si>
+  <si>
+    <t>eO6e0b4i93U</t>
+  </si>
+  <si>
+    <t>AlOvdFqlMxE</t>
+  </si>
+  <si>
+    <t>JM1S2ZkNVrQ</t>
+  </si>
+  <si>
+    <t>BlO34GiRoJ0</t>
+  </si>
+  <si>
+    <t>hm5nuQVrD1A</t>
+  </si>
+  <si>
+    <t>4OvywNsWWd4</t>
+  </si>
+  <si>
+    <t>G3ckelo2Vt8</t>
+  </si>
+  <si>
+    <t>1VA8v1btKdQ</t>
+  </si>
+  <si>
+    <t>S3ZaLXo0i-4</t>
+  </si>
+  <si>
+    <t>pSY3i5XHHXo</t>
+  </si>
+  <si>
+    <t>i_kF4zLNKio</t>
+  </si>
+  <si>
+    <t>AT-ElP8uSTE</t>
+  </si>
+  <si>
+    <t>3VUFM0x2rsU</t>
+  </si>
+  <si>
+    <t>yNGderoE76M</t>
+  </si>
+  <si>
+    <t>VkqiSzoVtUA</t>
+  </si>
+  <si>
+    <t>lcS9Fymo4V8</t>
+  </si>
+  <si>
+    <t>X52b-8y2Hf4</t>
+  </si>
+  <si>
+    <t>G5iGJHVtFqs</t>
+  </si>
+  <si>
+    <t>Hwybp38GnZw</t>
+  </si>
+  <si>
+    <t>i-sW4PfSxwA</t>
+  </si>
+  <si>
+    <t>wwB3FmbcC88</t>
+  </si>
+  <si>
+    <t>VlGtvN4fAIU</t>
+  </si>
+  <si>
+    <t>wfWIs2gFTAM</t>
+  </si>
+  <si>
+    <t>48h57PspBec</t>
+  </si>
+  <si>
+    <t>GvkeWZyx7_o</t>
+  </si>
+  <si>
+    <t>TLnUJzueBOQ</t>
+  </si>
+  <si>
+    <t>OqGH_6mLQjI</t>
+  </si>
+  <si>
+    <t>bWr-DA5Wjfw</t>
+  </si>
+  <si>
+    <t>pekzpzNCNDQ</t>
+  </si>
+  <si>
+    <t>g7rZTZBOrqQ</t>
+  </si>
+  <si>
+    <t>qb6UuECcPV0</t>
+  </si>
+  <si>
+    <t>Ez_4X3NMUiQ</t>
+  </si>
+  <si>
+    <t>Iig0kFj9Glg</t>
+  </si>
+  <si>
+    <t>BYDKK95cpfM</t>
+  </si>
+  <si>
+    <t>ierGU6fW3yI</t>
+  </si>
+  <si>
+    <t>YLMUzBzn4jI</t>
+  </si>
+  <si>
+    <t>51foBSsRpJk</t>
+  </si>
+  <si>
+    <t>bn0Kh9c4Zv4</t>
+  </si>
+  <si>
+    <t>FM7Z-Xq8Drc</t>
+  </si>
+  <si>
+    <t>MqFBlaMQKmw</t>
+  </si>
+  <si>
+    <t>F6nMSY3UaE0</t>
+  </si>
+  <si>
+    <t>QE-nO2-czUY</t>
+  </si>
+  <si>
+    <t>9BxKH-Iigpc</t>
+  </si>
+  <si>
+    <t>VRbkyEFCqZo</t>
+  </si>
+  <si>
     <t>NQypHE9_Fm4</t>
   </si>
   <si>
+    <t>2HCThr-qbPw</t>
+  </si>
+  <si>
+    <t>Su_SV29obhE</t>
+  </si>
+  <si>
+    <t>cKW-pp1pprg</t>
+  </si>
+  <si>
+    <t>HPJKxAhLw5I</t>
+  </si>
+  <si>
+    <t>K_CbgLpvH9E</t>
+  </si>
+  <si>
+    <t>sSFAi1dtKQc</t>
+  </si>
+  <si>
+    <t>FDZHzP-kvsY</t>
+  </si>
+  <si>
+    <t>-BxqibaPvCg</t>
+  </si>
+  <si>
+    <t>cgobX27KZRU</t>
+  </si>
+  <si>
+    <t>ayj57u38Oew</t>
+  </si>
+  <si>
+    <t>V1bd1ypBfw8</t>
+  </si>
+  <si>
+    <t>2HS3sFyywnM</t>
+  </si>
+  <si>
+    <t>7hTgjEzl4Bk</t>
+  </si>
+  <si>
+    <t>03ogf95osXw</t>
+  </si>
+  <si>
+    <t>jWwOTg35COs</t>
+  </si>
+  <si>
+    <t>eUi3mBPUpfE</t>
+  </si>
+  <si>
+    <t>GstoRIioBuQ</t>
+  </si>
+  <si>
+    <t>SVihhbs64aU</t>
+  </si>
+  <si>
+    <t>iYbV_GTY5k4</t>
+  </si>
+  <si>
+    <t>qJZ1Ez28C-A</t>
+  </si>
+  <si>
+    <t>GlUp3MCIQIk</t>
+  </si>
+  <si>
+    <t>AImXsv9ywmo</t>
+  </si>
+  <si>
+    <t>lGS6O47debI</t>
+  </si>
+  <si>
+    <t>A1pQ6xhHHbk</t>
+  </si>
+  <si>
+    <t>7LnBvuzjpr4</t>
+  </si>
+  <si>
+    <t>iogcY_4xGjo</t>
+  </si>
+  <si>
+    <t>VnV3emXRK9o</t>
+  </si>
+  <si>
+    <t>cV2gBU6hKfY</t>
+  </si>
+  <si>
+    <t>2OitFFCLfSw</t>
+  </si>
+  <si>
+    <t>y83x7MgzWOA</t>
+  </si>
+  <si>
+    <t>lOqO4F5FqWc</t>
+  </si>
+  <si>
+    <t>3olqrQtjPfc</t>
+  </si>
+  <si>
+    <t>V9XoKg3ODHM</t>
+  </si>
+  <si>
+    <t>oqLwCUlgMuw</t>
+  </si>
+  <si>
+    <t>ca54nGKw7w4</t>
+  </si>
+  <si>
+    <t>4TpLxUGcnbY</t>
+  </si>
+  <si>
+    <t>JI_Md14CH0Y</t>
+  </si>
+  <si>
+    <t>Y-N1R7U15Hs</t>
+  </si>
+  <si>
+    <t>MCV7j_aFFK4</t>
+  </si>
+  <si>
+    <t>C5DdPRcJoz8</t>
+  </si>
+  <si>
+    <t>tKg9KSpG0Vw</t>
+  </si>
+  <si>
+    <t>fIBIGRNH734</t>
+  </si>
+  <si>
+    <t>mxWIy8q_vQw</t>
+  </si>
+  <si>
+    <t>UNZqm3dxd2w</t>
+  </si>
+  <si>
+    <t>K2iuiPOLSfA</t>
+  </si>
+  <si>
+    <t>r4l9bFqgMaQ</t>
+  </si>
+  <si>
+    <t>zxYjTTXc-J8</t>
+  </si>
+  <si>
+    <t>gs6EwA3AVQ8</t>
+  </si>
+  <si>
+    <t>cl7w8QK7lic</t>
+  </si>
+  <si>
+    <t>steaizIyMn8</t>
+  </si>
+  <si>
+    <t>rPckDuTaSnw</t>
+  </si>
+  <si>
+    <t>ZPB-Ov4zA4g</t>
+  </si>
+  <si>
+    <t>nFFljO1fzJw</t>
+  </si>
+  <si>
+    <t>IvniOpFC860</t>
+  </si>
+  <si>
+    <t>iKUzhzustok</t>
+  </si>
+  <si>
+    <t>TDdEVBgDqK4</t>
+  </si>
+  <si>
+    <t>1mkpb6KV9NM</t>
+  </si>
+  <si>
+    <t>poH3td0GN4Y</t>
+  </si>
+  <si>
+    <t>_o__CTSeLz4</t>
+  </si>
+  <si>
+    <t>_9pPGIF-bqQ</t>
+  </si>
+  <si>
+    <t>0ONPlWHl9Gk</t>
+  </si>
+  <si>
+    <t>yPyFlO8G6rw</t>
+  </si>
+  <si>
+    <t>44-IpvZRfAw</t>
+  </si>
+  <si>
+    <t>y7Hyc3MRKno</t>
+  </si>
+  <si>
+    <t>onXn0YUmeWQ</t>
+  </si>
+  <si>
+    <t>Id1rwD0RU5k</t>
+  </si>
+  <si>
+    <t>92zPiKwr8i4</t>
+  </si>
+  <si>
+    <t>RqnbCPEXE-M</t>
+  </si>
+  <si>
+    <t>TwS4GTnrbUc</t>
+  </si>
+  <si>
+    <t>9gZLvy48-eA</t>
+  </si>
+  <si>
+    <t>ImO6sDdYB8U</t>
+  </si>
+  <si>
+    <t>rRin8TdvE1o</t>
+  </si>
+  <si>
+    <t>vRpN8yfNp7Y</t>
+  </si>
+  <si>
+    <t>jn73kYaLmKM</t>
+  </si>
+  <si>
+    <t>W8g5oohF4Q8</t>
+  </si>
+  <si>
+    <t>5qQdnhxI8Us</t>
+  </si>
+  <si>
+    <t>_2t18Hy9Z0Y</t>
+  </si>
+  <si>
+    <t>MrNcHCki8mE</t>
+  </si>
+  <si>
+    <t>kqphejRKaU0</t>
+  </si>
+  <si>
+    <t>Il0S8BoucSA</t>
+  </si>
+  <si>
+    <t>qEYdRDvqmcQ</t>
+  </si>
+  <si>
+    <t>UmTBOw5ITeU</t>
+  </si>
+  <si>
+    <t>LRr0MiIH8Sw</t>
+  </si>
+  <si>
+    <t>oxpEsowC2rY</t>
+  </si>
+  <si>
+    <t>EgLbYhnK30Y</t>
+  </si>
+  <si>
     <t>b8HbMzXeZa4</t>
   </si>
   <si>
-    <t>tKg9KSpG0Vw</t>
-  </si>
-  <si>
-    <t>vRpN8yfNp7Y</t>
-  </si>
-  <si>
-    <t>zAd6mDrJz-8</t>
+    <t>VZFjtKM_GtE</t>
+  </si>
+  <si>
+    <t>B9MwNFsIcxA</t>
+  </si>
+  <si>
+    <t>Pgwny1BiCYk</t>
+  </si>
+  <si>
+    <t>3Bi-0s8djNE</t>
+  </si>
+  <si>
+    <t>lgYfRGDiPDs</t>
+  </si>
+  <si>
+    <t>_MX7jvKoLsM</t>
+  </si>
+  <si>
+    <t>RFcK-myEqAo</t>
+  </si>
+  <si>
+    <t>esMX1x-E1Us</t>
+  </si>
+  <si>
+    <t>8yJXKYHg3mk</t>
+  </si>
+  <si>
+    <t>ZaCzkHkgrlc</t>
+  </si>
+  <si>
+    <t>ZNVuIU6UUiM</t>
+  </si>
+  <si>
+    <t>AHIlxaPZd5w</t>
+  </si>
+  <si>
+    <t>V1AtvYjTMQQ</t>
+  </si>
+  <si>
+    <t>Wk_lZXwa9K4</t>
+  </si>
+  <si>
+    <t>phaJXp_zMYM</t>
+  </si>
+  <si>
+    <t>tQOvOgm5Pdw</t>
+  </si>
+  <si>
+    <t>__bV5GzpgNw</t>
+  </si>
+  <si>
+    <t>UmzPf8GhQgE</t>
+  </si>
+  <si>
+    <t>ndAQfTzlVjc</t>
+  </si>
+  <si>
+    <t>Cvm85VWkNJg</t>
+  </si>
+  <si>
+    <t>ERUugjLmwuY</t>
+  </si>
+  <si>
+    <t>ol7Ca8n2xa8</t>
+  </si>
+  <si>
+    <t>hmdzniMJOZs</t>
+  </si>
+  <si>
+    <t>Jj-ni0inHqE</t>
+  </si>
+  <si>
+    <t>qKKNbYv3LrM</t>
+  </si>
+  <si>
+    <t>E4t9zVxHbNs</t>
+  </si>
+  <si>
+    <t>14OPT6CcsH4</t>
+  </si>
+  <si>
+    <t>9m1FCOHIIcA</t>
+  </si>
+  <si>
+    <t>3Ay2lS6tm4M</t>
+  </si>
+  <si>
+    <t>sWVPnyyLnFw</t>
+  </si>
+  <si>
+    <t>2WloJyW_NUQ</t>
+  </si>
+  <si>
+    <t>exI_hD_4jAM</t>
+  </si>
+  <si>
+    <t>u6wOyMUs74I</t>
+  </si>
+  <si>
+    <t>sxn5n89S7Xw</t>
+  </si>
+  <si>
+    <t>lp-EO5I60KA</t>
+  </si>
+  <si>
+    <t>Vkack7OKYjQ</t>
+  </si>
+  <si>
+    <t>mfxit90vWSs</t>
+  </si>
+  <si>
+    <t>PuxM0hR32GA</t>
+  </si>
+  <si>
+    <t>KJDEsAy9RyM</t>
+  </si>
+  <si>
+    <t>DaWcL3oOd-E</t>
+  </si>
+  <si>
+    <t>sf3PiPKlC8M</t>
+  </si>
+  <si>
+    <t>B9M4F_U1eEw</t>
+  </si>
+  <si>
+    <t>ez1cn8d28_8</t>
+  </si>
+  <si>
+    <t>QkfYX_4ZvNs</t>
+  </si>
+  <si>
+    <t>JX-yUUcJM2E</t>
+  </si>
+  <si>
+    <t>XxwJCrFhMA4</t>
+  </si>
+  <si>
+    <t>TK3ntJMwTVY</t>
+  </si>
+  <si>
+    <t>jXbXGkgT2Xg</t>
+  </si>
+  <si>
+    <t>BV4bTePsYHk</t>
+  </si>
+  <si>
+    <t>lJ7Ec3bKrxM</t>
+  </si>
+  <si>
+    <t>RubBzkZzpUA</t>
+  </si>
+  <si>
+    <t>1QpiJpvTtSw</t>
+  </si>
+  <si>
+    <t>qD0_yWgifDM</t>
+  </si>
+  <si>
+    <t>z8atGvZGEeo</t>
+  </si>
+  <si>
+    <t>4EZgfkAQ6xE</t>
+  </si>
+  <si>
+    <t>BElgcWsChSs</t>
+  </si>
+  <si>
+    <t>ffLd2pfU4Lw</t>
+  </si>
+  <si>
+    <t>356WoFm1z2I</t>
+  </si>
+  <si>
+    <t>ilbnRQE3tpw</t>
+  </si>
+  <si>
+    <t>uE10t-dGhGQ</t>
+  </si>
+  <si>
+    <t>TDtGX0iNnak</t>
+  </si>
+  <si>
+    <t>H7QEohOvGco</t>
+  </si>
+  <si>
+    <t>Vv6axHpSAjU</t>
+  </si>
+  <si>
+    <t>IuTDuvYr7f0</t>
+  </si>
+  <si>
+    <t>CxnJf0tWu48</t>
+  </si>
+  <si>
+    <t>3vUtRRZG0xY</t>
+  </si>
+  <si>
+    <t>wdzA1Z8tKek</t>
+  </si>
+  <si>
+    <t>_1btDc5xJe0</t>
+  </si>
+  <si>
+    <t>PEikGKDVsCc</t>
+  </si>
+  <si>
+    <t>JZjAg6fK-BQ</t>
+  </si>
+  <si>
+    <t>ffkaoXslwtI</t>
+  </si>
+  <si>
+    <t>eDuRoPIOBjE</t>
+  </si>
+  <si>
+    <t>wfCcs0vLysk</t>
+  </si>
+  <si>
+    <t>6fJI7xydShM</t>
+  </si>
+  <si>
+    <t>ouPsgmEKyww</t>
+  </si>
+  <si>
+    <t>BW_MAa5L9lg</t>
+  </si>
+  <si>
+    <t>At8v_Yc044Y</t>
+  </si>
+  <si>
+    <t>8PmM6SUn7Es</t>
+  </si>
+  <si>
+    <t>K0ibBPhiaG0</t>
+  </si>
+  <si>
+    <t>2Vuexl8rCNs</t>
+  </si>
+  <si>
+    <t>Fb_TTLo1fFg</t>
+  </si>
+  <si>
+    <t>Itbsnna09MY</t>
+  </si>
+  <si>
+    <t>bbBvzRWNQOQ</t>
+  </si>
+  <si>
+    <t>xdpABsJZQYU</t>
+  </si>
+  <si>
+    <t>EvsFBWUMrCw</t>
+  </si>
+  <si>
+    <t>x-axYKSh-jc</t>
+  </si>
+  <si>
+    <t>Xtq_A2NnHKQ</t>
+  </si>
+  <si>
+    <t>MmGzzlRNjFA</t>
+  </si>
+  <si>
+    <t>1CLhjDLUl4c</t>
+  </si>
+  <si>
+    <t>l0K4XPu3Qhg</t>
+  </si>
+  <si>
+    <t>NWSe2SoVwZs</t>
+  </si>
+  <si>
+    <t>l-mK3RUtZGs</t>
+  </si>
+  <si>
+    <t>kBdRlTmAx4Q</t>
+  </si>
+  <si>
+    <t>k7PmttZtFU0</t>
+  </si>
+  <si>
+    <t>aprGWX2IOGs</t>
+  </si>
+  <si>
+    <t>gTo-lPOGPdg</t>
+  </si>
+  <si>
+    <t>zJX_Oh4yVnc</t>
+  </si>
+  <si>
+    <t>QgOXIEhHU1Y</t>
+  </si>
+  <si>
+    <t>IdHWqTywbyA</t>
+  </si>
+  <si>
+    <t>iTRBRXOMzeM</t>
+  </si>
+  <si>
+    <t>kgBdQyxhjEY</t>
+  </si>
+  <si>
+    <t>o7FmGwoDJvc</t>
+  </si>
+  <si>
+    <t>4SL11QJZzCI</t>
+  </si>
+  <si>
+    <t>hMp5yi7yaHI</t>
+  </si>
+  <si>
+    <t>r7zJ8srwwjk</t>
+  </si>
+  <si>
+    <t>GQTVVs0BSKw</t>
+  </si>
+  <si>
+    <t>3he4lvoghMg</t>
+  </si>
+  <si>
+    <t>S1ABZywPONY</t>
+  </si>
+  <si>
+    <t>gHzuabZUd6c</t>
+  </si>
+  <si>
+    <t>2lTB1pIg1y0</t>
+  </si>
+  <si>
+    <t>r93mofOZuI4</t>
+  </si>
+  <si>
+    <t>9bqk6ZUsKyA</t>
+  </si>
+  <si>
+    <t>jOjJY3xEI8o</t>
+  </si>
+  <si>
+    <t>QzRW6bfv3Fo</t>
+  </si>
+  <si>
+    <t>UCN569Pb-gk</t>
+  </si>
+  <si>
+    <t>97X8RqFvZIk</t>
+  </si>
+  <si>
+    <t>uqv-oC-Izi8</t>
+  </si>
+  <si>
+    <t>DPdRR0Ng0BY</t>
+  </si>
+  <si>
+    <t>PwRCZE0-P2I</t>
+  </si>
+  <si>
+    <t>lwbjAKQKmoM</t>
+  </si>
+  <si>
+    <t>WMSpjDc8zH8</t>
+  </si>
+  <si>
+    <t>IFmPrQmGgGA</t>
+  </si>
+  <si>
+    <t>2nUGLtfiTbk</t>
+  </si>
+  <si>
+    <t>03_Tby_ICCw</t>
+  </si>
+  <si>
+    <t>_bhXh1KxVHc</t>
+  </si>
+  <si>
+    <t>am3QB_ID4Lc</t>
+  </si>
+  <si>
+    <t>fxhOPqLLyKg</t>
+  </si>
+  <si>
+    <t>aslFiO7vThQ</t>
+  </si>
+  <si>
+    <t>vKeCr-MAyH4</t>
+  </si>
+  <si>
+    <t>-ne1thvJDeE</t>
+  </si>
+  <si>
+    <t>aUq1TmEFegQ</t>
+  </si>
+  <si>
+    <t>EHS5b3F0q60</t>
+  </si>
+  <si>
+    <t>SZpiiixlHWY</t>
+  </si>
+  <si>
+    <t>Oi1lvJS4uS8</t>
+  </si>
+  <si>
+    <t>tWYsfOSY9vY</t>
+  </si>
+  <si>
+    <t>iD2rhdFRehU</t>
+  </si>
+  <si>
+    <t>FUVGGwO2Y8A</t>
+  </si>
+  <si>
+    <t>DkzQxw16G9w</t>
+  </si>
+  <si>
+    <t>FOjdXSrtUxA</t>
+  </si>
+  <si>
+    <t>PzHZGefMx9Q</t>
+  </si>
+  <si>
+    <t>SfGCd_7LHpQ</t>
+  </si>
+  <si>
+    <t>qr10OS7UJxY</t>
+  </si>
+  <si>
+    <t>pk5tFczY224</t>
+  </si>
+  <si>
+    <t>u6Q8ywGzkAI</t>
+  </si>
+  <si>
+    <t>hxEe2wSe_zc</t>
+  </si>
+  <si>
+    <t>jJUvn-i73zI</t>
+  </si>
+  <si>
+    <t>JsoKwtvAZc8</t>
+  </si>
+  <si>
+    <t>WhaTru5czpA</t>
+  </si>
+  <si>
+    <t>W7661YW0FH4</t>
+  </si>
+  <si>
+    <t>Q0TpWitfxPk</t>
+  </si>
+  <si>
+    <t>L3ibkV6t0NM</t>
+  </si>
+  <si>
+    <t>2XhVg38cDTU</t>
+  </si>
+  <si>
+    <t>EVbdbVhzcM4</t>
+  </si>
+  <si>
+    <t>01FuE1RnajY</t>
+  </si>
+  <si>
+    <t>oMmpC1tef4c</t>
+  </si>
+  <si>
+    <t>kJQP7kiw5Fk</t>
+  </si>
+  <si>
+    <t>y90R8BPc8Ag</t>
+  </si>
+  <si>
+    <t>TgHcTailbao</t>
+  </si>
+  <si>
+    <t>CRuOOxF-ENQ</t>
+  </si>
+  <si>
+    <t>nSI_2yvBAIU</t>
+  </si>
+  <si>
+    <t>VtIyrJCfhk4</t>
+  </si>
+  <si>
+    <t>tnTPaLOaHz8</t>
+  </si>
+  <si>
+    <t>CRTmcafIDiQ</t>
+  </si>
+  <si>
+    <t>AYJAJWCS8eM</t>
+  </si>
+  <si>
+    <t>KkCXLABwHP0</t>
+  </si>
+  <si>
+    <t>ylhcZZ7O3Tk</t>
+  </si>
+  <si>
+    <t>F7hOWHis2zk</t>
+  </si>
+  <si>
+    <t>5UE2kT5LxE0</t>
+  </si>
+  <si>
+    <t>Qs0KZwhKdwo</t>
+  </si>
+  <si>
+    <t>XfqOB4hvxlY</t>
+  </si>
+  <si>
+    <t>LT7yiHRUAkA</t>
+  </si>
+  <si>
+    <t>1AbFi_OrhrY</t>
+  </si>
+  <si>
+    <t>LsW1lL6-ELU</t>
+  </si>
+  <si>
+    <t>Cqg8tQH4U8M</t>
+  </si>
+  <si>
+    <t>YLt73w6criQ</t>
+  </si>
+  <si>
+    <t>yhB3BgJyGl8</t>
+  </si>
+  <si>
+    <t>VkL832e2rXQ</t>
+  </si>
+  <si>
+    <t>Y-W-w8yNiKU</t>
+  </si>
+  <si>
+    <t>yObM3AESlKY</t>
+  </si>
+  <si>
+    <t>DPDUDPCttfc</t>
+  </si>
+  <si>
+    <t>F-OU8gr2htQ</t>
+  </si>
+  <si>
+    <t>0VM88nLZK0w</t>
+  </si>
+  <si>
+    <t>MAm0RLQpYas</t>
+  </si>
+  <si>
+    <t>4ZzpL8BCKPw</t>
+  </si>
+  <si>
+    <t>5E1d_wA3B1g</t>
+  </si>
+  <si>
+    <t>_eUlpPY96Ok</t>
+  </si>
+  <si>
+    <t>YhwvvYOE_Nk</t>
+  </si>
+  <si>
+    <t>3ryID_SwU5E</t>
+  </si>
+  <si>
+    <t>nSNkwIvlWJU</t>
+  </si>
+  <si>
+    <t>js3OoEgDSMQ</t>
+  </si>
+  <si>
+    <t>ZzFoNe5rNMo</t>
+  </si>
+  <si>
+    <t>s93NCuXt7x4</t>
+  </si>
+  <si>
+    <t>vyB_2BnouRs</t>
+  </si>
+  <si>
+    <t>KOEfDvr4DcQ</t>
+  </si>
+  <si>
+    <t>-PXAOZwvv04</t>
+  </si>
+  <si>
+    <t>7O43VDOlQ_o</t>
+  </si>
+  <si>
+    <t>tt_D5pbJxmA</t>
+  </si>
+  <si>
+    <t>sbCvQbBi2G8</t>
+  </si>
+  <si>
+    <t>GO6QNV6Ua_0</t>
+  </si>
+  <si>
+    <t>OLY6SzP08jg</t>
+  </si>
+  <si>
+    <t>EGBLSbeiEzs</t>
+  </si>
+  <si>
+    <t>vjqt8T3tJIE</t>
+  </si>
+  <si>
+    <t>7GGzc3x9WJU</t>
+  </si>
+  <si>
+    <t>1AMFwO7BGW8</t>
+  </si>
+  <si>
+    <t>mEsAlDPy9H0</t>
+  </si>
+  <si>
+    <t>nK8IqQbOskI</t>
+  </si>
+  <si>
+    <t>61Xlain6QP8</t>
+  </si>
+  <si>
+    <t>5NxOpIslAPw</t>
+  </si>
+  <si>
+    <t>yn8DNmNzVuA</t>
+  </si>
+  <si>
+    <t>0e3GPea1Tyg</t>
+  </si>
+  <si>
+    <t>jNkNnQ7AfT8</t>
+  </si>
+  <si>
+    <t>fMfipiV_17o</t>
+  </si>
+  <si>
+    <t>OMYoyny6psU</t>
+  </si>
+  <si>
+    <t>2dCdfcraDB0</t>
+  </si>
+  <si>
+    <t>Urcw56iV3EI</t>
+  </si>
+  <si>
+    <t>LjliKhPLxHk</t>
+  </si>
+  <si>
+    <t>RuWcetR4cog</t>
+  </si>
+  <si>
+    <t>a002hwAqLDw</t>
+  </si>
+  <si>
+    <t>i2PsXT88UeU</t>
+  </si>
+  <si>
+    <t>WNW1xRqbt94</t>
+  </si>
+  <si>
+    <t>iTs0zGNCsOs</t>
+  </si>
+  <si>
+    <t>XFqYOK6LSsY</t>
+  </si>
+  <si>
+    <t>m4QFk2Pa9CU</t>
+  </si>
+  <si>
+    <t>s_EHezMKD7Q</t>
+  </si>
+  <si>
+    <t>k5Yvhn8OI3M</t>
+  </si>
+  <si>
+    <t>8nilP--GFLY</t>
+  </si>
+  <si>
+    <t>BD08USRd2M8</t>
+  </si>
+  <si>
+    <t>o7-x4DTz_Sg</t>
+  </si>
+  <si>
+    <t>KSpDrwlvBvY</t>
+  </si>
+  <si>
+    <t>cF1Na4AIecM</t>
+  </si>
+  <si>
+    <t>IGZdpB35_fM</t>
+  </si>
+  <si>
+    <t>51BNn5Ojupw</t>
+  </si>
+  <si>
+    <t>LXvv6CbGg8A</t>
+  </si>
+  <si>
+    <t>907sfCJCFvk</t>
+  </si>
+  <si>
+    <t>4vfIC0dZ8jM</t>
+  </si>
+  <si>
+    <t>gU_bqeXeK-A</t>
+  </si>
+  <si>
+    <t>elVF7oG0pQs</t>
+  </si>
+  <si>
+    <t>f-M3JN_7LGU</t>
+  </si>
+  <si>
+    <t>-VPYbJxPvzY</t>
+  </si>
+  <si>
+    <t>m5zhPegPUc8</t>
+  </si>
+  <si>
+    <t>5qBDQgfeB6s</t>
+  </si>
+  <si>
+    <t>krsBRQbOPQ4</t>
+  </si>
+  <si>
+    <t>RXnwGwNZZJg</t>
+  </si>
+  <si>
+    <t>9Me-OzXuSMo</t>
+  </si>
+  <si>
+    <t>L2cbT3elGl8</t>
+  </si>
+  <si>
+    <t>Ha80ZaecGkQ</t>
+  </si>
+  <si>
+    <t>h4UqMyldS7Q</t>
+  </si>
+  <si>
+    <t>HkGyb6GXMo0</t>
+  </si>
+  <si>
+    <t>f1Ub9Zku0lI</t>
+  </si>
+  <si>
+    <t>vUeV3gc_JZ0</t>
+  </si>
+  <si>
+    <t>8a5Z1Idf-Jo</t>
+  </si>
+  <si>
+    <t>AnaASTBn_K4</t>
+  </si>
+  <si>
+    <t>ymvjfu_Hm_8</t>
+  </si>
+  <si>
+    <t>sBaB1bcOgVE</t>
+  </si>
+  <si>
+    <t>9uZ-jeZS8d0</t>
+  </si>
+  <si>
+    <t>1uLi1I3G2N4</t>
+  </si>
+  <si>
+    <t>8DNQ8DYgCJE</t>
+  </si>
+  <si>
+    <t>IfhMILe8C84</t>
+  </si>
+  <si>
+    <t>uYFtWVv5F3E</t>
+  </si>
+  <si>
+    <t>ec7pM-n-5ts</t>
+  </si>
+  <si>
+    <t>tlYcUqEPN58</t>
+  </si>
+  <si>
+    <t>zHL9GP_B30E</t>
+  </si>
+  <si>
+    <t>5VEto1CcHVE</t>
+  </si>
+  <si>
+    <t>VoqmR5b5zB0</t>
+  </si>
+  <si>
+    <t>RqQGUJK7Na4</t>
+  </si>
+  <si>
+    <t>qshNkIvF-Oc</t>
+  </si>
+  <si>
+    <t>M4-L8UgPkOk</t>
+  </si>
+  <si>
+    <t>3t195yz9xCc</t>
+  </si>
+  <si>
+    <t>e91M0XLX7Jw</t>
+  </si>
+  <si>
+    <t>9__i1VDK8EM</t>
+  </si>
+  <si>
+    <t>pSNUHygTD7k</t>
+  </si>
+  <si>
+    <t>sY6BGVE-PBE</t>
+  </si>
+  <si>
+    <t>i9RFjLrYxfk</t>
+  </si>
+  <si>
+    <t>VVljQ9JccsY</t>
+  </si>
+  <si>
+    <t>mhmGwTDpPf0</t>
+  </si>
+  <si>
+    <t>77kpv3BHHg0</t>
+  </si>
+  <si>
+    <t>8fxbUQhx0Hk</t>
+  </si>
+  <si>
+    <t>Gk6RF5k3C2M</t>
+  </si>
+  <si>
+    <t>o8hO9R_Xs7Q</t>
+  </si>
+  <si>
+    <t>3Jgev_YGl44</t>
+  </si>
+  <si>
+    <t>hcehrylhJoI</t>
+  </si>
+  <si>
+    <t>erWTsWut7Vc</t>
+  </si>
+  <si>
+    <t>CCSGelSCPGE</t>
+  </si>
+  <si>
+    <t>kuUZYUBHryw</t>
+  </si>
+  <si>
+    <t>PoJMeCrqi4o</t>
+  </si>
+  <si>
+    <t>AetGXMcNU3M</t>
+  </si>
+  <si>
+    <t>XX1-nL9oM2E</t>
+  </si>
+  <si>
+    <t>mo5361CqFGs</t>
+  </si>
+  <si>
+    <t>3yA3PNcILlc</t>
+  </si>
+  <si>
+    <t>-ibLmPuojmw</t>
+  </si>
+  <si>
+    <t>D9Z9zBmL-VM</t>
+  </si>
+  <si>
+    <t>0Z54mw8cD1I</t>
+  </si>
+  <si>
+    <t>LWHMtkbCxd0</t>
+  </si>
+  <si>
+    <t>qL1kRHtOtJg</t>
+  </si>
+  <si>
+    <t>8ZYD4cD3yHw</t>
+  </si>
+  <si>
+    <t>EX_FfND3q7c</t>
+  </si>
+  <si>
+    <t>vGr1tvjqWs0</t>
+  </si>
+  <si>
+    <t>6ltU9q1pKKM</t>
+  </si>
+  <si>
+    <t>BWplLa3BBX0</t>
+  </si>
+  <si>
+    <t>DX5wxit-5Yo</t>
+  </si>
+  <si>
+    <t>1VLtwB7CPGw</t>
+  </si>
+  <si>
+    <t>W2xZxYaGlfs</t>
+  </si>
+  <si>
+    <t>8woxWlkxuis</t>
+  </si>
+  <si>
+    <t>ifVk1E5My7M</t>
+  </si>
+  <si>
+    <t>Yd6gYHBXD-I</t>
+  </si>
+  <si>
+    <t>tFaF6VRYcpw</t>
+  </si>
+  <si>
+    <t>_ArVh3Cj9rw</t>
+  </si>
+  <si>
+    <t>8CfWTV5kQUM</t>
+  </si>
+  <si>
+    <t>HYYoepuLZSI</t>
+  </si>
+  <si>
+    <t>mvoMShXqwtQ</t>
+  </si>
+  <si>
+    <t>btFETPVpDcw</t>
+  </si>
+  <si>
+    <t>lEBtXFhpwO4</t>
+  </si>
+  <si>
+    <t>YDdN4vm_59c</t>
+  </si>
+  <si>
+    <t>_G3bic1kp0o</t>
+  </si>
+  <si>
+    <t>N3ftBeP16TA</t>
+  </si>
+  <si>
+    <t>hN0xpuih8zo</t>
+  </si>
+  <si>
+    <t>YJQSuUZdcV4</t>
+  </si>
+  <si>
+    <t>KMfaYskgQlc</t>
+  </si>
+  <si>
+    <t>jCIf07qU_mQ</t>
+  </si>
+  <si>
+    <t>lqIpDyrJndw</t>
+  </si>
+  <si>
+    <t>JAjxq93njvs</t>
+  </si>
+  <si>
+    <t>UxU3RceDIn0</t>
+  </si>
+  <si>
+    <t>RYE26pF0tLk</t>
+  </si>
+  <si>
+    <t>GYbFc91SJHE</t>
+  </si>
+  <si>
+    <t>f4_ZPwvKF5g</t>
+  </si>
+  <si>
+    <t>trydrfj__uY</t>
+  </si>
+  <si>
+    <t>-U8-cSX1pHQ</t>
+  </si>
+  <si>
+    <t>8ZwhtDXhzUc</t>
+  </si>
+  <si>
+    <t>ro5arbsZfMs</t>
+  </si>
+  <si>
+    <t>FEy5F2_ikG4</t>
+  </si>
+  <si>
+    <t>lOKASgtr6kU</t>
+  </si>
+  <si>
+    <t>vxfNnfyEagE</t>
+  </si>
+  <si>
+    <t>Y1E6R13YD1Y</t>
+  </si>
+  <si>
+    <t>g9wlrjt3vPY</t>
+  </si>
+  <si>
+    <t>N29-54dhVHg</t>
+  </si>
+  <si>
+    <t>awpU69Jy-CQ</t>
+  </si>
+  <si>
+    <t>3hGe5Yk_Lyg</t>
+  </si>
+  <si>
+    <t>h3Kii3q2ZVU</t>
+  </si>
+  <si>
+    <t>Pzz4Z-O7710</t>
+  </si>
+  <si>
+    <t>qwrzGqhaotE</t>
+  </si>
+  <si>
+    <t>04kGIbHUIho</t>
+  </si>
+  <si>
+    <t>DWCl2dN6hpg</t>
+  </si>
+  <si>
+    <t>4Do_Z1PXUW4</t>
+  </si>
+  <si>
+    <t>pfbilhs5dt4</t>
+  </si>
+  <si>
+    <t>t8rMgGSgHv0</t>
+  </si>
+  <si>
+    <t>qZHycHI3F1Q</t>
+  </si>
+  <si>
+    <t>3BLoozf3MlM</t>
+  </si>
+  <si>
+    <t>hBNWInRS6hM</t>
+  </si>
+  <si>
+    <t>10FfGGdCcJ4</t>
+  </si>
+  <si>
+    <t>6cnpRCUWhMY</t>
+  </si>
+  <si>
+    <t>19IdcJU8524</t>
+  </si>
+  <si>
+    <t>mmzy05r9ZE0</t>
+  </si>
+  <si>
+    <t>c1tjh_ZO_tY</t>
+  </si>
+  <si>
+    <t>VQpTVVsNHQs</t>
+  </si>
+  <si>
+    <t>IHDX1eVP-_Q</t>
+  </si>
+  <si>
+    <t>UOKQqKE_I30</t>
+  </si>
+  <si>
+    <t>_JZom_gVfuw</t>
+  </si>
+  <si>
+    <t>4g89b_lUOl8</t>
+  </si>
+  <si>
+    <t>qeJ6fqiDQ30</t>
+  </si>
+  <si>
+    <t>iqIuaen3TJs</t>
+  </si>
+  <si>
+    <t>w7djgxcJ68M</t>
+  </si>
+  <si>
+    <t>GnByKoTgSg0</t>
+  </si>
+  <si>
+    <t>0UhVwaPfhHM</t>
+  </si>
+  <si>
+    <t>qa5-mKVSQHQ</t>
+  </si>
+  <si>
+    <t>6TALoEUNdOU</t>
+  </si>
+  <si>
+    <t>jjqV55VWoxA</t>
+  </si>
+  <si>
+    <t>p8DHWcZcKLU</t>
+  </si>
+  <si>
+    <t>0fhAJjhZuJw</t>
+  </si>
+  <si>
+    <t>7Q3rPzzZJLs</t>
+  </si>
+  <si>
+    <t>u-z5139CW1I</t>
+  </si>
+  <si>
+    <t>owZiOi3KD58</t>
+  </si>
+  <si>
+    <t>OGiBcHF-wOU</t>
+  </si>
+  <si>
+    <t>dkf9LNwo2kM</t>
+  </si>
+  <si>
+    <t>xNNSn2UVUHc</t>
+  </si>
+  <si>
+    <t>3VJT2JeDCyw</t>
+  </si>
+  <si>
+    <t>fN-PCjiAs7k</t>
+  </si>
+  <si>
+    <t>OFk5xdqruxs</t>
+  </si>
+  <si>
+    <t>VxjbtDGgkt4</t>
+  </si>
+  <si>
+    <t>OU1vo8xQSm8</t>
+  </si>
+  <si>
+    <t>9FiIkT3WkWg</t>
+  </si>
+  <si>
+    <t>eN3D7UoKhWQ</t>
+  </si>
+  <si>
+    <t>gyO5zhBI9U8</t>
+  </si>
+  <si>
+    <t>yt0XYibFwaY</t>
+  </si>
+  <si>
+    <t>Z6RG5jrZQCE</t>
+  </si>
+  <si>
+    <t>23g5HBOg3Ic</t>
+  </si>
+  <si>
+    <t>MJtIjupffDk</t>
+  </si>
+  <si>
+    <t>g_M60l2VALI</t>
+  </si>
+  <si>
+    <t>u7ldP7XezL0</t>
+  </si>
+  <si>
+    <t>aweKJRi2N1A</t>
+  </si>
+  <si>
+    <t>2W85Dwxx218</t>
+  </si>
+  <si>
+    <t>GFyHfJeiyAY</t>
+  </si>
+  <si>
+    <t>wamtTEVFDiA</t>
+  </si>
+  <si>
+    <t>9OM6x4U65EY</t>
+  </si>
+  <si>
+    <t>cluFg58suOg</t>
+  </si>
+  <si>
+    <t>K2H7qqKjVVQ</t>
+  </si>
+  <si>
+    <t>J6kAtdwNJ5s</t>
+  </si>
+  <si>
+    <t>2hsn7AxXKmg</t>
+  </si>
+  <si>
+    <t>mj0XInqZMHY</t>
+  </si>
+  <si>
+    <t>et8Cn9q_A-g</t>
+  </si>
+  <si>
+    <t>m-EL5Fti1TM</t>
+  </si>
+  <si>
+    <t>Er2IIYpGgS0</t>
+  </si>
+  <si>
+    <t>EDap9qxb96k</t>
+  </si>
+  <si>
+    <t>uY5oF0tZiWI</t>
+  </si>
+  <si>
+    <t>H8Jwu-9ud-A</t>
+  </si>
+  <si>
+    <t>GLoeAJUcz38</t>
+  </si>
+  <si>
+    <t>p7EiT9tKiig</t>
+  </si>
+  <si>
+    <t>jZwGVuA8PMI</t>
+  </si>
+  <si>
+    <t>pVEo_mckBIc</t>
+  </si>
+  <si>
+    <t>GurljGjfrVs</t>
+  </si>
+  <si>
+    <t>snvUzd_aZFQ</t>
+  </si>
+  <si>
+    <t>kcZbFvm4FDw</t>
+  </si>
+  <si>
+    <t>idD57Hd3mJI</t>
+  </si>
+  <si>
+    <t>XdnX-4oqCwQ</t>
+  </si>
+  <si>
+    <t>VKJZ4PCWgY8</t>
+  </si>
+  <si>
+    <t>5njBrlE6Ux0</t>
+  </si>
+  <si>
+    <t>_Gma4TPZCXg</t>
+  </si>
+  <si>
+    <t>G5_YyZUOQL8</t>
+  </si>
+  <si>
+    <t>P_kRTqaD8Mc</t>
+  </si>
+  <si>
+    <t>5tQPftbhCVo</t>
+  </si>
+  <si>
+    <t>_SMgIXwknwA</t>
+  </si>
+  <si>
+    <t>Ok54QynuSqU</t>
+  </si>
+  <si>
+    <t>96ix3P9WaRc</t>
+  </si>
+  <si>
+    <t>mBvuq4ijT7o</t>
+  </si>
+  <si>
+    <t>Z0L0xWZhYTE</t>
+  </si>
+  <si>
+    <t>0dgq4ZkjQCA</t>
+  </si>
+  <si>
+    <t>gnhub9-KLsE</t>
+  </si>
+  <si>
+    <t>ftbQz0MfSmo</t>
+  </si>
+  <si>
+    <t>qQYVCdHIcTY</t>
+  </si>
+  <si>
+    <t>j2_dJY_mIys</t>
+  </si>
+  <si>
+    <t>_mrr3UNALww</t>
+  </si>
+  <si>
+    <t>rxJx5c2zQCg</t>
+  </si>
+  <si>
+    <t>sZKqH8ddifQ</t>
+  </si>
+  <si>
+    <t>yec-UUauUV8</t>
+  </si>
+  <si>
+    <t>Nlod_2qX91I</t>
+  </si>
+  <si>
+    <t>WVOiDcFUg_I</t>
+  </si>
+  <si>
+    <t>IEN39uKOYeU</t>
+  </si>
+  <si>
+    <t>MiUHjLxm3V0</t>
+  </si>
+  <si>
+    <t>jEWaLRi_G60</t>
+  </si>
+  <si>
+    <t>1yMozrDEqbg</t>
+  </si>
+  <si>
+    <t>RR0yM5mG_8U</t>
+  </si>
+  <si>
+    <t>HilsrscQr9o</t>
+  </si>
+  <si>
+    <t>baP-7_O_Fn8</t>
+  </si>
+  <si>
+    <t>L4B7z8dHDRc</t>
+  </si>
+  <si>
+    <t>klKVm1FALhs</t>
+  </si>
+  <si>
+    <t>16RX6rKJle8</t>
+  </si>
+  <si>
+    <t>p7SWgstujAg</t>
+  </si>
+  <si>
+    <t>s8agLHxTLjQ</t>
+  </si>
+  <si>
+    <t>ETPccfEzqRI</t>
+  </si>
+  <si>
+    <t>KrLj6nc516A</t>
+  </si>
+  <si>
+    <t>NlLUVeNZxKs</t>
+  </si>
+  <si>
+    <t>NdEM_eY8w8E</t>
+  </si>
+  <si>
+    <t>0wxBHxpMFXA</t>
+  </si>
+  <si>
+    <t>at-vRIQA_PU</t>
+  </si>
+  <si>
+    <t>u4NnQuMdSTU</t>
+  </si>
+  <si>
+    <t>16YnOUnbE6s</t>
+  </si>
+  <si>
+    <t>xTsREJ6KEfg</t>
+  </si>
+  <si>
+    <t>PyDlfAw10E4</t>
+  </si>
+  <si>
+    <t>EGPoXOLspfo</t>
+  </si>
+  <si>
+    <t>nclPaVQmCHc</t>
+  </si>
+  <si>
+    <t>bCb1umZaaFQ</t>
+  </si>
+  <si>
+    <t>1WEAJ-DFkHE</t>
+  </si>
+  <si>
+    <t>TjKoGrJ-FuY</t>
+  </si>
+  <si>
+    <t>87gWaABqGYs</t>
+  </si>
+  <si>
+    <t>Mb6H7trzMfI</t>
+  </si>
+  <si>
+    <t>Dj2jioqD-Hw</t>
+  </si>
+  <si>
+    <t>yFO2pRHAEqw</t>
+  </si>
+  <si>
+    <t>0c0DExZ3oT4</t>
+  </si>
+  <si>
+    <t>fx0d0G-qvYk</t>
+  </si>
+  <si>
+    <t>mD4jp2HHu0g</t>
+  </si>
+  <si>
+    <t>-yrZpTHBEss</t>
+  </si>
+  <si>
+    <t>yHr29IpYpRU</t>
+  </si>
+  <si>
+    <t>pUwVZUOSTvk</t>
+  </si>
+  <si>
+    <t>UAWcs5H-qgQ</t>
+  </si>
+  <si>
+    <t>L-PkACES1qc</t>
+  </si>
+  <si>
+    <t>WTOm65IZneg</t>
+  </si>
+  <si>
+    <t>vHYeChEf2lA</t>
+  </si>
+  <si>
+    <t>mwKJfNYwvm8</t>
+  </si>
+  <si>
+    <t>dXaIkbvJdYM</t>
   </si>
   <si>
     <t>qyTBSJyDLlQ</t>
   </si>
   <si>
-    <t>09JYAZEoOOk</t>
-  </si>
-  <si>
-    <t>9OM6x4U65EY</t>
-  </si>
-  <si>
-    <t>xqYb1hMQKV4</t>
-  </si>
-  <si>
-    <t>HYYoepuLZSI</t>
+    <t>oA6ciBCYl4w</t>
+  </si>
+  <si>
+    <t>Cw29h7LhEuE</t>
+  </si>
+  <si>
+    <t>DdPWX4RqDOY</t>
+  </si>
+  <si>
+    <t>w-253j0BjLk</t>
+  </si>
+  <si>
+    <t>bMGoMu-CxMY</t>
+  </si>
+  <si>
+    <t>8KYdQpiU4zU</t>
+  </si>
+  <si>
+    <t>-F9nCQtxkRw</t>
+  </si>
+  <si>
+    <t>Fdyi9Dw6B5A</t>
+  </si>
+  <si>
+    <t>W7H5zzV8wbU</t>
+  </si>
+  <si>
+    <t>erLbbextvlY</t>
+  </si>
+  <si>
+    <t>WSOqOv68UsU</t>
+  </si>
+  <si>
+    <t>uo9t_BrhsMQ</t>
+  </si>
+  <si>
+    <t>jVTuz6h_beA</t>
+  </si>
+  <si>
+    <t>c1iKcBaFTA0</t>
+  </si>
+  <si>
+    <t>3zJoCpvKhx4</t>
+  </si>
+  <si>
+    <t>O6mZnetxUX8</t>
+  </si>
+  <si>
+    <t>2SY9tlZ5_20</t>
+  </si>
+  <si>
+    <t>efBB0D4tf1Y</t>
+  </si>
+  <si>
+    <t>xS11-GIemXY</t>
+  </si>
+  <si>
+    <t>LZYfSYXY-go</t>
+  </si>
+  <si>
+    <t>BNGjKDFAGTA</t>
+  </si>
+  <si>
+    <t>yXWw0_UfSFg</t>
   </si>
   <si>
     <t>zMNAos1hotI</t>
   </si>
   <si>
-    <t>4ZzpL8BCKPw</t>
-  </si>
-  <si>
-    <t>61Xlain6QP8</t>
-  </si>
-  <si>
-    <t>5E1d_wA3B1g</t>
-  </si>
-  <si>
-    <t>aprGWX2IOGs</t>
-  </si>
-  <si>
-    <t>F-OU8gr2htQ</t>
-  </si>
-  <si>
-    <t>VZFjtKM_GtE</t>
-  </si>
-  <si>
-    <t>NWSe2SoVwZs</t>
-  </si>
-  <si>
-    <t>Wk_lZXwa9K4</t>
-  </si>
-  <si>
-    <t>Urcw56iV3EI</t>
-  </si>
-  <si>
-    <t>8ZYD4cD3yHw</t>
-  </si>
-  <si>
-    <t>DHR6usutswA</t>
-  </si>
-  <si>
-    <t>zPbrkmdcTfo</t>
-  </si>
-  <si>
-    <t>UxU3RceDIn0</t>
-  </si>
-  <si>
-    <t>8ZwhtDXhzUc</t>
-  </si>
-  <si>
-    <t>EGPoXOLspfo</t>
-  </si>
-  <si>
-    <t>S3ZaLXo0i-4</t>
-  </si>
-  <si>
-    <t>f1Ub9Zku0lI</t>
-  </si>
-  <si>
-    <t>TtgUzJsXq6U</t>
-  </si>
-  <si>
-    <t>SZpiiixlHWY</t>
-  </si>
-  <si>
-    <t>cF1Na4AIecM</t>
-  </si>
-  <si>
-    <t>NdEM_eY8w8E</t>
-  </si>
-  <si>
-    <t>2HCThr-qbPw</t>
-  </si>
-  <si>
-    <t>hxEe2wSe_zc</t>
-  </si>
-  <si>
-    <t>GnByKoTgSg0</t>
-  </si>
-  <si>
-    <t>EGBLSbeiEzs</t>
-  </si>
-  <si>
-    <t>Ez_4X3NMUiQ</t>
-  </si>
-  <si>
-    <t>KMfaYskgQlc</t>
-  </si>
-  <si>
-    <t>aslFiO7vThQ</t>
-  </si>
-  <si>
-    <t>3hGe5Yk_Lyg</t>
-  </si>
-  <si>
-    <t>4Do_Z1PXUW4</t>
-  </si>
-  <si>
-    <t>CRuOOxF-ENQ</t>
-  </si>
-  <si>
-    <t>qL1kRHtOtJg</t>
-  </si>
-  <si>
-    <t>mEsAlDPy9H0</t>
-  </si>
-  <si>
-    <t>txk--OgckSQ</t>
-  </si>
-  <si>
-    <t>klKVm1FALhs</t>
-  </si>
-  <si>
-    <t>afWnfwNagx8</t>
-  </si>
-  <si>
-    <t>BElgcWsChSs</t>
-  </si>
-  <si>
-    <t>oqLwCUlgMuw</t>
-  </si>
-  <si>
-    <t>kuUZYUBHryw</t>
-  </si>
-  <si>
-    <t>XX1-nL9oM2E</t>
-  </si>
-  <si>
-    <t>r93mofOZuI4</t>
-  </si>
-  <si>
-    <t>TDdEVBgDqK4</t>
-  </si>
-  <si>
-    <t>XGFnZ-xGHsg</t>
-  </si>
-  <si>
-    <t>XxwJCrFhMA4</t>
-  </si>
-  <si>
-    <t>4DgTtRIvPvE</t>
-  </si>
-  <si>
-    <t>LGVOJA-VSRo</t>
-  </si>
-  <si>
-    <t>3VUFM0x2rsU</t>
-  </si>
-  <si>
-    <t>awpU69Jy-CQ</t>
-  </si>
-  <si>
-    <t>inlj61TsIRw</t>
-  </si>
-  <si>
-    <t>ETPccfEzqRI</t>
-  </si>
-  <si>
-    <t>356WoFm1z2I</t>
-  </si>
-  <si>
-    <t>VoqmR5b5zB0</t>
-  </si>
-  <si>
-    <t>5NxOpIslAPw</t>
-  </si>
-  <si>
-    <t>eoHqgAJgxOc</t>
-  </si>
-  <si>
-    <t>Z6RG5jrZQCE</t>
-  </si>
-  <si>
-    <t>RyfqcA5RF4c</t>
-  </si>
-  <si>
-    <t>iTs0zGNCsOs</t>
-  </si>
-  <si>
-    <t>4g89b_lUOl8</t>
-  </si>
-  <si>
-    <t>OFk5xdqruxs</t>
-  </si>
-  <si>
-    <t>gU_bqeXeK-A</t>
-  </si>
-  <si>
-    <t>_Y2smOELBxk</t>
-  </si>
-  <si>
-    <t>cgCSasQU_ew</t>
-  </si>
-  <si>
-    <t>tQOvOgm5Pdw</t>
-  </si>
-  <si>
-    <t>VnV3emXRK9o</t>
-  </si>
-  <si>
-    <t>uo9t_BrhsMQ</t>
-  </si>
-  <si>
-    <t>1QpiJpvTtSw</t>
-  </si>
-  <si>
-    <t>2SY9tlZ5_20</t>
-  </si>
-  <si>
-    <t>ffLd2pfU4Lw</t>
-  </si>
-  <si>
-    <t>qTjA2L3j5Po</t>
-  </si>
-  <si>
-    <t>kcZbFvm4FDw</t>
-  </si>
-  <si>
-    <t>p8DHWcZcKLU</t>
-  </si>
-  <si>
-    <t>biyH0s6tbAU</t>
-  </si>
-  <si>
-    <t>m4QFk2Pa9CU</t>
-  </si>
-  <si>
-    <t>wURhR2Vtm8E</t>
-  </si>
-  <si>
-    <t>G3ckelo2Vt8</t>
-  </si>
-  <si>
-    <t>Fdyi9Dw6B5A</t>
-  </si>
-  <si>
-    <t>o7-x4DTz_Sg</t>
-  </si>
-  <si>
-    <t>aUq1TmEFegQ</t>
-  </si>
-  <si>
-    <t>OHkRYXwD87A</t>
-  </si>
-  <si>
-    <t>_SMgIXwknwA</t>
-  </si>
-  <si>
-    <t>0Z54mw8cD1I</t>
-  </si>
-  <si>
-    <t>aweKJRi2N1A</t>
-  </si>
-  <si>
-    <t>DX5wxit-5Yo</t>
-  </si>
-  <si>
-    <t>3yA3PNcILlc</t>
-  </si>
-  <si>
-    <t>AlOvdFqlMxE</t>
-  </si>
-  <si>
-    <t>RXnwGwNZZJg</t>
-  </si>
-  <si>
-    <t>lOqO4F5FqWc</t>
-  </si>
-  <si>
-    <t>0fhAJjhZuJw</t>
-  </si>
-  <si>
-    <t>NlLUVeNZxKs</t>
-  </si>
-  <si>
-    <t>0c0DExZ3oT4</t>
-  </si>
-  <si>
-    <t>c1iKcBaFTA0</t>
-  </si>
-  <si>
-    <t>fN-PCjiAs7k</t>
-  </si>
-  <si>
-    <t>ifVk1E5My7M</t>
-  </si>
-  <si>
-    <t>GQTVVs0BSKw</t>
-  </si>
-  <si>
-    <t>FseDdBrkhK4</t>
-  </si>
-  <si>
-    <t>8woxWlkxuis</t>
-  </si>
-  <si>
-    <t>yNGderoE76M</t>
-  </si>
-  <si>
-    <t>rCjJItWMxqI</t>
-  </si>
-  <si>
-    <t>4EZgfkAQ6xE</t>
-  </si>
-  <si>
-    <t>qeJ6fqiDQ30</t>
-  </si>
-  <si>
-    <t>pSNUHygTD7k</t>
-  </si>
-  <si>
-    <t>IFmPrQmGgGA</t>
-  </si>
-  <si>
-    <t>1VLtwB7CPGw</t>
-  </si>
-  <si>
-    <t>UOKQqKE_I30</t>
-  </si>
-  <si>
-    <t>kgBdQyxhjEY</t>
-  </si>
-  <si>
-    <t>yFO2pRHAEqw</t>
-  </si>
-  <si>
-    <t>yQN4LqcLAgA</t>
-  </si>
-  <si>
-    <t>PoJMeCrqi4o</t>
-  </si>
-  <si>
-    <t>RFcK-myEqAo</t>
-  </si>
-  <si>
-    <t>FEy5F2_ikG4</t>
-  </si>
-  <si>
-    <t>9-llcas2hOE</t>
-  </si>
-  <si>
-    <t>cluFg58suOg</t>
-  </si>
-  <si>
-    <t>GvkeWZyx7_o</t>
-  </si>
-  <si>
-    <t>PyDlfAw10E4</t>
-  </si>
-  <si>
-    <t>zRzR0So7Ans</t>
-  </si>
-  <si>
-    <t>8yJXKYHg3mk</t>
-  </si>
-  <si>
-    <t>AImXsv9ywmo</t>
-  </si>
-  <si>
-    <t>lcS9Fymo4V8</t>
-  </si>
-  <si>
-    <t>pMRxeZAKWvk</t>
-  </si>
-  <si>
-    <t>V1AtvYjTMQQ</t>
-  </si>
-  <si>
-    <t>Yd6gYHBXD-I</t>
-  </si>
-  <si>
-    <t>s8agLHxTLjQ</t>
-  </si>
-  <si>
-    <t>EHS5b3F0q60</t>
-  </si>
-  <si>
-    <t>VxjbtDGgkt4</t>
-  </si>
-  <si>
-    <t>QS87RLjFE_g</t>
-  </si>
-  <si>
-    <t>yt0XYibFwaY</t>
-  </si>
-  <si>
-    <t>K2iuiPOLSfA</t>
-  </si>
-  <si>
-    <t>kBdRlTmAx4Q</t>
-  </si>
-  <si>
-    <t>a3w3C6ATGrY</t>
-  </si>
-  <si>
-    <t>wON9BvL_Lyw</t>
-  </si>
-  <si>
-    <t>EvsFBWUMrCw</t>
-  </si>
-  <si>
-    <t>yObM3AESlKY</t>
-  </si>
-  <si>
-    <t>qr10OS7UJxY</t>
-  </si>
-  <si>
-    <t>96ix3P9WaRc</t>
-  </si>
-  <si>
-    <t>moTRUU4MRPM</t>
-  </si>
-  <si>
-    <t>s_EHezMKD7Q</t>
-  </si>
-  <si>
-    <t>1mkpb6KV9NM</t>
-  </si>
-  <si>
-    <t>esMX1x-E1Us</t>
-  </si>
-  <si>
-    <t>HilsrscQr9o</t>
-  </si>
-  <si>
-    <t>am3QB_ID4Lc</t>
-  </si>
-  <si>
-    <t>5njBrlE6Ux0</t>
-  </si>
-  <si>
-    <t>W7H5zzV8wbU</t>
-  </si>
-  <si>
-    <t>OMYoyny6psU</t>
-  </si>
-  <si>
-    <t>Itbsnna09MY</t>
-  </si>
-  <si>
-    <t>Jj-ni0inHqE</t>
-  </si>
-  <si>
-    <t>OLY6SzP08jg</t>
-  </si>
-  <si>
-    <t>z8atGvZGEeo</t>
-  </si>
-  <si>
-    <t>pk5tFczY224</t>
-  </si>
-  <si>
-    <t>OU1vo8xQSm8</t>
-  </si>
-  <si>
-    <t>g9wlrjt3vPY</t>
-  </si>
-  <si>
-    <t>uK6RaiZdzCo</t>
-  </si>
-  <si>
-    <t>9gZLvy48-eA</t>
-  </si>
-  <si>
-    <t>jgliCvYQ4hY</t>
-  </si>
-  <si>
-    <t>wdzA1Z8tKek</t>
-  </si>
-  <si>
-    <t>vHYeChEf2lA</t>
-  </si>
-  <si>
-    <t>_2t18Hy9Z0Y</t>
-  </si>
-  <si>
-    <t>QzRW6bfv3Fo</t>
-  </si>
-  <si>
-    <t>BD08USRd2M8</t>
-  </si>
-  <si>
-    <t>jZwGVuA8PMI</t>
-  </si>
-  <si>
-    <t>qa5-mKVSQHQ</t>
-  </si>
-  <si>
-    <t>jXbXGkgT2Xg</t>
-  </si>
-  <si>
-    <t>cyURNr9LZdM</t>
-  </si>
-  <si>
-    <t>51BNn5Ojupw</t>
-  </si>
-  <si>
-    <t>LsW1lL6-ELU</t>
-  </si>
-  <si>
-    <t>PuxM0hR32GA</t>
-  </si>
-  <si>
-    <t>ol7Ca8n2xa8</t>
-  </si>
-  <si>
-    <t>vGr1tvjqWs0</t>
-  </si>
-  <si>
-    <t>imrloYMePL0</t>
-  </si>
-  <si>
-    <t>2hsn7AxXKmg</t>
-  </si>
-  <si>
-    <t>yPyFlO8G6rw</t>
-  </si>
-  <si>
-    <t>3zJoCpvKhx4</t>
-  </si>
-  <si>
-    <t>iTRBRXOMzeM</t>
-  </si>
-  <si>
-    <t>lGS6O47debI</t>
-  </si>
-  <si>
-    <t>wjWMOYLNK_E</t>
-  </si>
-  <si>
-    <t>klHr7F_xIig</t>
-  </si>
-  <si>
-    <t>qEYdRDvqmcQ</t>
-  </si>
-  <si>
-    <t>xdpABsJZQYU</t>
-  </si>
-  <si>
-    <t>AK3HbkbgiQA</t>
-  </si>
-  <si>
-    <t>sBaB1bcOgVE</t>
-  </si>
-  <si>
-    <t>h_kGwBANynQ</t>
-  </si>
-  <si>
-    <t>9m1FCOHIIcA</t>
-  </si>
-  <si>
-    <t>6cnpRCUWhMY</t>
-  </si>
-  <si>
-    <t>BltXeMM96DA</t>
-  </si>
-  <si>
-    <t>yec-UUauUV8</t>
-  </si>
-  <si>
-    <t>VRbkyEFCqZo</t>
-  </si>
-  <si>
-    <t>0bCWJjW7SgA</t>
-  </si>
-  <si>
-    <t>h3Kii3q2ZVU</t>
-  </si>
-  <si>
-    <t>AetGXMcNU3M</t>
-  </si>
-  <si>
-    <t>a002hwAqLDw</t>
-  </si>
-  <si>
-    <t>f4_ZPwvKF5g</t>
-  </si>
-  <si>
-    <t>COWxTAPkr_k</t>
-  </si>
-  <si>
-    <t>v9n6wYBq4HI</t>
-  </si>
-  <si>
-    <t>ylhcZZ7O3Tk</t>
-  </si>
-  <si>
-    <t>Oi1lvJS4uS8</t>
-  </si>
-  <si>
-    <t>CYobbeiGgp8</t>
-  </si>
-  <si>
-    <t>_P7wHN_kOv4</t>
-  </si>
-  <si>
-    <t>X52b-8y2Hf4</t>
-  </si>
-  <si>
-    <t>3Ay2lS6tm4M</t>
-  </si>
-  <si>
-    <t>7O43VDOlQ_o</t>
-  </si>
-  <si>
-    <t>Gk6RF5k3C2M</t>
-  </si>
-  <si>
-    <t>sv71JMZEpYY</t>
-  </si>
-  <si>
-    <t>QHorNUuEXc0</t>
-  </si>
-  <si>
-    <t>jWwOTg35COs</t>
-  </si>
-  <si>
-    <t>01FuE1RnajY</t>
-  </si>
-  <si>
-    <t>P_kRTqaD8Mc</t>
-  </si>
-  <si>
-    <t>s93NCuXt7x4</t>
-  </si>
-  <si>
-    <t>Il0S8BoucSA</t>
-  </si>
-  <si>
-    <t>UAWcs5H-qgQ</t>
-  </si>
-  <si>
-    <t>K0ibBPhiaG0</t>
-  </si>
-  <si>
-    <t>iD2rhdFRehU</t>
-  </si>
-  <si>
-    <t>u6wOyMUs74I</t>
-  </si>
-  <si>
-    <t>FOjdXSrtUxA</t>
-  </si>
-  <si>
-    <t>mKEphyIbtXo</t>
-  </si>
-  <si>
-    <t>mo5361CqFGs</t>
-  </si>
-  <si>
-    <t>wfWIs2gFTAM</t>
-  </si>
-  <si>
-    <t>pekzpzNCNDQ</t>
-  </si>
-  <si>
-    <t>mj0XInqZMHY</t>
-  </si>
-  <si>
-    <t>UPOT2tgY9QQ</t>
-  </si>
-  <si>
-    <t>y83x7MgzWOA</t>
-  </si>
-  <si>
-    <t>k6ZoE4RrcDs</t>
-  </si>
-  <si>
-    <t>23g5HBOg3Ic</t>
-  </si>
-  <si>
-    <t>87gWaABqGYs</t>
-  </si>
-  <si>
-    <t>lp-EO5I60KA</t>
-  </si>
-  <si>
-    <t>tlYcUqEPN58</t>
-  </si>
-  <si>
-    <t>WNW1xRqbt94</t>
-  </si>
-  <si>
-    <t>3t195yz9xCc</t>
-  </si>
-  <si>
-    <t>7LnBvuzjpr4</t>
-  </si>
-  <si>
-    <t>cimoNqiulUE</t>
-  </si>
-  <si>
-    <t>RubBzkZzpUA</t>
-  </si>
-  <si>
-    <t>2lTB1pIg1y0</t>
-  </si>
-  <si>
-    <t>eDuRoPIOBjE</t>
-  </si>
-  <si>
-    <t>BYDKK95cpfM</t>
-  </si>
-  <si>
-    <t>Ha80ZaecGkQ</t>
-  </si>
-  <si>
-    <t>JAjxq93njvs</t>
-  </si>
-  <si>
-    <t>Bi0taCrL22Q</t>
-  </si>
-  <si>
-    <t>Vkack7OKYjQ</t>
-  </si>
-  <si>
-    <t>o7FmGwoDJvc</t>
-  </si>
-  <si>
-    <t>jJUvn-i73zI</t>
-  </si>
-  <si>
-    <t>1AMFwO7BGW8</t>
-  </si>
-  <si>
-    <t>8DkcTriimSM</t>
-  </si>
-  <si>
-    <t>G5iGJHVtFqs</t>
-  </si>
-  <si>
-    <t>Mh5dKiiZRlg</t>
-  </si>
-  <si>
-    <t>3he4lvoghMg</t>
-  </si>
-  <si>
-    <t>xTsREJ6KEfg</t>
-  </si>
-  <si>
-    <t>kaqxOKmq0ZI</t>
-  </si>
-  <si>
-    <t>muT3_bTXR_w</t>
-  </si>
-  <si>
-    <t>5tQPftbhCVo</t>
-  </si>
-  <si>
-    <t>tivtBueDg_c</t>
-  </si>
-  <si>
-    <t>k7PmttZtFU0</t>
-  </si>
-  <si>
-    <t>m5zhPegPUc8</t>
-  </si>
-  <si>
-    <t>Su_SV29obhE</t>
-  </si>
-  <si>
-    <t>UmTBOw5ITeU</t>
-  </si>
-  <si>
-    <t>Er2IIYpGgS0</t>
-  </si>
-  <si>
-    <t>ouPsgmEKyww</t>
-  </si>
-  <si>
-    <t>19IdcJU8524</t>
-  </si>
-  <si>
-    <t>G5_YyZUOQL8</t>
-  </si>
-  <si>
-    <t>jCIf07qU_mQ</t>
-  </si>
-  <si>
-    <t>xhIFmxslJCQ</t>
-  </si>
-  <si>
-    <t>L3ibkV6t0NM</t>
-  </si>
-  <si>
-    <t>4vfIC0dZ8jM</t>
-  </si>
-  <si>
-    <t>MrNcHCki8mE</t>
-  </si>
-  <si>
-    <t>YDdN4vm_59c</t>
-  </si>
-  <si>
-    <t>u6Q8ywGzkAI</t>
-  </si>
-  <si>
-    <t>DdPWX4RqDOY</t>
-  </si>
-  <si>
-    <t>YSrjyXqA5cM</t>
-  </si>
-  <si>
-    <t>jn73kYaLmKM</t>
-  </si>
-  <si>
-    <t>2HS3sFyywnM</t>
-  </si>
-  <si>
-    <t>O6mZnetxUX8</t>
-  </si>
-  <si>
-    <t>vyB_2BnouRs</t>
-  </si>
-  <si>
-    <t>x-axYKSh-jc</t>
-  </si>
-  <si>
-    <t>2nUGLtfiTbk</t>
-  </si>
-  <si>
-    <t>qb6UuECcPV0</t>
-  </si>
-  <si>
-    <t>YpUgnlZkPEI</t>
-  </si>
-  <si>
-    <t>WMSpjDc8zH8</t>
-  </si>
-  <si>
-    <t>sxn5n89S7Xw</t>
-  </si>
-  <si>
-    <t>VKJZ4PCWgY8</t>
-  </si>
-  <si>
-    <t>Bd2fE3YO7Aw</t>
-  </si>
-  <si>
-    <t>4SL11QJZzCI</t>
-  </si>
-  <si>
-    <t>0ONPlWHl9Gk</t>
-  </si>
-  <si>
-    <t>L-PkACES1qc</t>
-  </si>
-  <si>
-    <t>o8hO9R_Xs7Q</t>
-  </si>
-  <si>
-    <t>Qs0KZwhKdwo</t>
-  </si>
-  <si>
-    <t>moSE2_ur994</t>
-  </si>
-  <si>
-    <t>BlO34GiRoJ0</t>
-  </si>
-  <si>
-    <t>JM1S2ZkNVrQ</t>
-  </si>
-  <si>
-    <t>L4B7z8dHDRc</t>
-  </si>
-  <si>
-    <t>cKW-pp1pprg</t>
-  </si>
-  <si>
-    <t>sWVPnyyLnFw</t>
-  </si>
-  <si>
-    <t>DPDUDPCttfc</t>
-  </si>
-  <si>
-    <t>OGiBcHF-wOU</t>
-  </si>
-  <si>
-    <t>VkqiSzoVtUA</t>
-  </si>
-  <si>
-    <t>Id1rwD0RU5k</t>
-  </si>
-  <si>
-    <t>AHIlxaPZd5w</t>
-  </si>
-  <si>
-    <t>mxWIy8q_vQw</t>
-  </si>
-  <si>
-    <t>ro5arbsZfMs</t>
-  </si>
-  <si>
-    <t>goCGfcCjtSo</t>
-  </si>
-  <si>
-    <t>MAm0RLQpYas</t>
-  </si>
-  <si>
-    <t>qKKNbYv3LrM</t>
-  </si>
-  <si>
-    <t>vO4QeHR9SXM</t>
-  </si>
-  <si>
-    <t>w-253j0BjLk</t>
-  </si>
-  <si>
-    <t>hddRxBhGiMI</t>
-  </si>
-  <si>
-    <t>YqKYpgZ9FWU</t>
-  </si>
-  <si>
-    <t>gTo-lPOGPdg</t>
-  </si>
-  <si>
-    <t>PzHZGefMx9Q</t>
-  </si>
-  <si>
-    <t>btFETPVpDcw</t>
-  </si>
-  <si>
-    <t>nSNkwIvlWJU</t>
-  </si>
-  <si>
-    <t>LWHMtkbCxd0</t>
-  </si>
-  <si>
-    <t>YJOmxjtG9IM</t>
-  </si>
-  <si>
-    <t>jEWaLRi_G60</t>
-  </si>
-  <si>
-    <t>GlUp3MCIQIk</t>
-  </si>
-  <si>
-    <t>OqGH_6mLQjI</t>
-  </si>
-  <si>
-    <t>S1ABZywPONY</t>
-  </si>
-  <si>
-    <t>eO6e0b4i93U</t>
-  </si>
-  <si>
-    <t>1CLhjDLUl4c</t>
-  </si>
-  <si>
-    <t>xDi_TTbk3-c</t>
-  </si>
-  <si>
-    <t>Z0L0xWZhYTE</t>
-  </si>
-  <si>
-    <t>t8rMgGSgHv0</t>
-  </si>
-  <si>
-    <t>sJj3q6njVbM</t>
-  </si>
-  <si>
-    <t>ImO6sDdYB8U</t>
-  </si>
-  <si>
-    <t>3Bi-0s8djNE</t>
-  </si>
-  <si>
-    <t>04kGIbHUIho</t>
-  </si>
-  <si>
-    <t>Y1E6R13YD1Y</t>
-  </si>
-  <si>
-    <t>7hTgjEzl4Bk</t>
-  </si>
-  <si>
-    <t>BW_MAa5L9lg</t>
-  </si>
-  <si>
-    <t>16RX6rKJle8</t>
-  </si>
-  <si>
-    <t>hN0xpuih8zo</t>
-  </si>
-  <si>
-    <t>mcTpep5uoZ8</t>
-  </si>
-  <si>
-    <t>uqv-oC-Izi8</t>
-  </si>
-  <si>
-    <t>_bhXh1KxVHc</t>
-  </si>
-  <si>
-    <t>nSI_2yvBAIU</t>
-  </si>
-  <si>
-    <t>8a5Z1Idf-Jo</t>
-  </si>
-  <si>
-    <t>dkf9LNwo2kM</t>
+    <t>K8O3bpR4mdQ</t>
+  </si>
+  <si>
+    <t>v9UxwWXWhNE</t>
   </si>
 </sst>
 </file>
@@ -1427,11 +2767,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A351"/>
+  <dimension ref="A1:A795"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="17.88671875" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -1570,12 +2907,12 @@
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.3">
@@ -1845,1347 +3182,3567 @@
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>59</v>
+        <v>87</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
     </row>
     <row r="180" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
     </row>
     <row r="181" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
     </row>
     <row r="182" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
     </row>
     <row r="183" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
     </row>
     <row r="184" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
     </row>
     <row r="185" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
     </row>
     <row r="186" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
     </row>
     <row r="187" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
     </row>
     <row r="188" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
     <row r="189" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
     </row>
     <row r="190" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
     </row>
     <row r="191" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
     </row>
     <row r="192" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
     </row>
     <row r="194" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
     </row>
     <row r="195" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
     </row>
     <row r="198" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
     </row>
     <row r="199" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
     </row>
     <row r="200" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
     </row>
     <row r="201" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
     </row>
     <row r="202" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
     </row>
     <row r="203" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
     </row>
     <row r="204" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
     </row>
     <row r="205" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
     </row>
     <row r="206" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
     </row>
     <row r="207" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
     </row>
     <row r="208" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
     </row>
     <row r="209" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
     </row>
     <row r="210" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
     </row>
     <row r="211" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="212" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
     </row>
     <row r="213" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="214" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
     </row>
     <row r="215" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
     </row>
     <row r="216" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="217" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="218" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
     </row>
     <row r="219" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
     </row>
     <row r="220" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
     </row>
     <row r="221" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
     </row>
     <row r="222" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="223" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
     </row>
     <row r="224" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="225" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
     </row>
     <row r="226" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
     </row>
     <row r="227" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
     </row>
     <row r="228" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
     </row>
     <row r="229" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
     </row>
     <row r="230" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
     </row>
     <row r="231" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
     </row>
     <row r="232" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
     </row>
     <row r="233" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
     </row>
     <row r="234" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
     </row>
     <row r="235" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
     </row>
     <row r="236" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
     </row>
     <row r="237" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
     </row>
     <row r="238" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
     </row>
     <row r="239" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
     </row>
     <row r="240" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
     </row>
     <row r="241" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
     </row>
     <row r="242" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
     </row>
     <row r="243" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
     </row>
     <row r="244" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
     </row>
     <row r="245" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
     </row>
     <row r="246" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
     </row>
     <row r="247" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
     </row>
     <row r="248" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
     </row>
     <row r="249" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
     </row>
     <row r="250" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
     </row>
     <row r="251" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
     </row>
     <row r="252" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
     </row>
     <row r="253" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
     </row>
     <row r="254" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
     </row>
     <row r="255" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
     </row>
     <row r="256" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
     </row>
     <row r="257" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
     </row>
     <row r="258" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
     </row>
     <row r="259" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
     </row>
     <row r="260" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
     </row>
     <row r="261" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
     </row>
     <row r="262" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
     </row>
     <row r="263" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
     </row>
     <row r="264" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
     </row>
     <row r="265" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
     </row>
     <row r="266" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
     </row>
     <row r="267" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
     </row>
     <row r="268" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="269" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
     </row>
     <row r="270" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
     </row>
     <row r="271" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
     </row>
     <row r="272" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
     </row>
     <row r="273" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
     </row>
     <row r="274" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
     </row>
     <row r="275" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="276" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
     </row>
     <row r="277" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
     </row>
     <row r="278" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
     </row>
     <row r="279" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
     </row>
     <row r="280" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
     </row>
     <row r="281" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
     </row>
     <row r="282" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
     </row>
     <row r="283" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
     </row>
     <row r="284" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
     </row>
     <row r="285" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
     </row>
     <row r="286" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
     </row>
     <row r="287" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
     </row>
     <row r="288" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
     </row>
     <row r="289" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
     </row>
     <row r="290" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
     </row>
     <row r="291" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
     </row>
     <row r="292" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
     </row>
     <row r="293" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
     </row>
     <row r="294" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="295" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
     </row>
     <row r="296" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
     </row>
     <row r="297" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
     </row>
     <row r="298" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="299" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
     </row>
     <row r="300" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="301" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="302" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
     </row>
     <row r="303" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
     </row>
     <row r="304" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
     </row>
     <row r="305" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
     </row>
     <row r="306" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="307" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
     </row>
     <row r="308" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
     </row>
     <row r="309" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
     </row>
     <row r="310" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
     </row>
     <row r="311" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
     </row>
     <row r="312" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
     </row>
     <row r="313" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>39</v>
+        <v>312</v>
       </c>
     </row>
     <row r="314" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
     </row>
     <row r="315" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
     </row>
     <row r="316" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
     </row>
     <row r="317" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
     </row>
     <row r="318" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
     </row>
     <row r="319" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
     </row>
     <row r="320" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
     </row>
     <row r="321" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
     </row>
     <row r="322" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
     </row>
     <row r="323" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
     </row>
     <row r="324" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
     </row>
     <row r="325" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
     </row>
     <row r="326" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
     </row>
     <row r="327" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
     </row>
     <row r="328" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
     </row>
     <row r="329" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
     </row>
     <row r="330" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="331" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
     </row>
     <row r="332" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
     </row>
     <row r="333" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
     </row>
     <row r="334" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
     </row>
     <row r="335" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
     </row>
     <row r="336" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
     </row>
     <row r="337" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
     </row>
     <row r="338" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
     </row>
     <row r="339" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
     </row>
     <row r="340" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
     </row>
     <row r="341" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
     </row>
     <row r="342" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
     </row>
     <row r="343" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
     </row>
     <row r="344" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
     </row>
     <row r="345" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
     </row>
     <row r="346" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
     </row>
     <row r="347" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
     </row>
     <row r="348" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
     </row>
     <row r="349" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
     </row>
     <row r="350" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
     </row>
     <row r="351" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
-        <v>343</v>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="352" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A352" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="353" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A353" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="354" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A354" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="355" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A355" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="356" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A356" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="357" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A357" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="358" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A358" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="359" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A359" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="360" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A360" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="361" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A361" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="362" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A362" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="363" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A363" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="364" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A364" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="365" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A365" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="366" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A366" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="367" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A367" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="368" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A368" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="369" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A369" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="370" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A370" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="371" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A371" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="372" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A372" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="373" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A373" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="374" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A374" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="375" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A375" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="376" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A376" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="377" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A377" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="378" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A378" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="379" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A379" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="380" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A380" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="381" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A381" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="382" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A382" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="383" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A383" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="384" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A384" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="385" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A385" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="386" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A386" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="387" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A387" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="388" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A388" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="389" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A389" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="390" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A390" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="391" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A391" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="392" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A392" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="393" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A393" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="394" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A394" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="395" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A395" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="396" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A396" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="397" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A397" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="398" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A398" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="399" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A399" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="400" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A400" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="401" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A401" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="402" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A402" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="403" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A403" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="404" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A404" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="405" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A405" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="406" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A406" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="407" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A407" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="408" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A408" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="409" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A409" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="410" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A410" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="411" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A411" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="412" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A412" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="413" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A413" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="414" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A414" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="415" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A415" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="416" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A416" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="417" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A417" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="418" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A418" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="419" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A419" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="420" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A420" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="421" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A421" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="422" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A422" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="423" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A423" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="424" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A424" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="425" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A425" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="426" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A426" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="427" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A427" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="428" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A428" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="429" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A429" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="430" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A430" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="431" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A431" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="432" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A432" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="433" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A433" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="434" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A434" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="435" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A435" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="436" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A436" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="437" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A437" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="438" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A438" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="439" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A439" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="440" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A440" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="441" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A441" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="442" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A442" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="443" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A443" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="444" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A444" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="445" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A445" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="446" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A446" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="447" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A447" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="448" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A448" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="449" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A449" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="450" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A450" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="451" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A451" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="452" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A452" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="453" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A453" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="454" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A454" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="455" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A455" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="456" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A456" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="457" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A457" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="458" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A458" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="459" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A459" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="460" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A460" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="461" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A461" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="462" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A462" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="463" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A463" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="464" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A464" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="465" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A465" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="466" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A466" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="467" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A467" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="468" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A468" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="469" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A469" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="470" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A470" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="471" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A471" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="472" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A472" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="473" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A473" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="474" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A474" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="475" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A475" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="476" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A476" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="477" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A477" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="478" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A478" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="479" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A479" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="480" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A480" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="481" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A481" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="482" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A482" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="483" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A483" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="484" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A484" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="485" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A485" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="486" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A486" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="487" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A487" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="488" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A488" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="489" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A489" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="490" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A490" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="491" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A491" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="492" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A492" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="493" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A493" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="494" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A494" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="495" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A495" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="496" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A496" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="497" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A497" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="498" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A498" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="499" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A499" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="500" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A500" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="501" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A501" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="502" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A502" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="503" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A503" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="504" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A504" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="505" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A505" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="506" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A506" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="507" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A507" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="508" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A508" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="509" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A509" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="510" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A510" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="511" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A511" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="512" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A512" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="513" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A513" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="514" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A514" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="515" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A515" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="516" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A516" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="517" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A517" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="518" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A518" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="519" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A519" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="520" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A520" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="521" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A521" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="522" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A522" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="523" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A523" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="524" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A524" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="525" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A525" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="526" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A526" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="527" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A527" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="528" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A528" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="529" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A529" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="530" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A530" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="531" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A531" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="532" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A532" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="533" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A533" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="534" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A534" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="535" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A535" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="536" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A536" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="537" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A537" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="538" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A538" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="539" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A539" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="540" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A540" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="541" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A541" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="542" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A542" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="543" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A543" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="544" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A544" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="545" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A545" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="546" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A546" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="547" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A547" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="548" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A548" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="549" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A549" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="550" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A550" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="551" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A551" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="552" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A552" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="553" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A553" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="554" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A554" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="555" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A555" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="556" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A556" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="557" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A557" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="558" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A558" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="559" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A559" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="560" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A560" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="561" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A561" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="562" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A562" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="563" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A563" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="564" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A564" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="565" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A565" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="566" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A566" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="567" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A567" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="568" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A568" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="569" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A569" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="570" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A570" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="571" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A571" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="572" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A572" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="573" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A573" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="574" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A574" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="575" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A575" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="576" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A576" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="577" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A577" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="578" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A578" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="579" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A579" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="580" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A580" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="581" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A581" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="582" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A582" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="583" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A583" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="584" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A584" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="585" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A585" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="586" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A586" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="587" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A587" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="588" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A588" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="589" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A589" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="590" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A590" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="591" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A591" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="592" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A592" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="593" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A593" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="594" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A594" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="595" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A595" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="596" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A596" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="597" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A597" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="598" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A598" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="599" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A599" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="600" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A600" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="601" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A601" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="602" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A602" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="603" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A603" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="604" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A604" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="605" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A605" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="606" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A606" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="607" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A607" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="608" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A608" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="609" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A609" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="610" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A610" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="611" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A611" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="612" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A612" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="613" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A613" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="614" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A614" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="615" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A615" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="616" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A616" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="617" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A617" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="618" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A618" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="619" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A619" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="620" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A620" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="621" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A621" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="622" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A622" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="623" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A623" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="624" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A624" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="625" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A625" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="626" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A626" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="627" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A627" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="628" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A628" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="629" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A629" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="630" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A630" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="631" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A631" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="632" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A632" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="633" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A633" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="634" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A634" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="635" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A635" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="636" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A636" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="637" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A637" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="638" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A638" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="639" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A639" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="640" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A640" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="641" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A641" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="642" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A642" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="643" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A643" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="644" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A644" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="645" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A645" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="646" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A646" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="647" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A647" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="648" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A648" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="649" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A649" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="650" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A650" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="651" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A651" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="652" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A652" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="653" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A653" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="654" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A654" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="655" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A655" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="656" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A656" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="657" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A657" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="658" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A658" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="659" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A659" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="660" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A660" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="661" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A661" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="662" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A662" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="663" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A663" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="664" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A664" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="665" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A665" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="666" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A666" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="667" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A667" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="668" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A668" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="669" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A669" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="670" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A670" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="671" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A671" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="672" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A672" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="673" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A673" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="674" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A674" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="675" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A675" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="676" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A676" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="677" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A677" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="678" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A678" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="679" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A679" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="680" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A680" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="681" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A681" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="682" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A682" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="683" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A683" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="684" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A684" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="685" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A685" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="686" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A686" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="687" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A687" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="688" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A688" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="689" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A689" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="690" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A690" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="691" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A691" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="692" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A692" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="693" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A693" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="694" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A694" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="695" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A695" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="696" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A696" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="697" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A697" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="698" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A698" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="699" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A699" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="700" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A700" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="701" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A701" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="702" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A702" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="703" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A703" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="704" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A704" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="705" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A705" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="706" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A706" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="707" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A707" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="708" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A708" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="709" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A709" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="710" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A710" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="711" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A711" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="712" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A712" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="713" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A713" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="714" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A714" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="715" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A715" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="716" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A716" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="717" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A717" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="718" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A718" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="719" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A719" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="720" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A720" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="721" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A721" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="722" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A722" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="723" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A723" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="724" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A724" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="725" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A725" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="726" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A726" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="727" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A727" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="728" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A728" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="729" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A729" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="730" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A730" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="731" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A731" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="732" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A732" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="733" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A733" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="734" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A734" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="735" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A735" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="736" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A736" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="737" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A737" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="738" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A738" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="739" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A739" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="740" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A740" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="741" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A741" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="742" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A742" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="743" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A743" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="744" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A744" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="745" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A745" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="746" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A746" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="747" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A747" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="748" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A748" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="749" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A749" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="750" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A750" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="751" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A751" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="752" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A752" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="753" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A753" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="754" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A754" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="755" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A755" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="756" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A756" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="757" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A757" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="758" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A758" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="759" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A759" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="760" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A760" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="761" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A761" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="762" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A762" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="763" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A763" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="764" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A764" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="765" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A765" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="766" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A766" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="767" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A767" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="768" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A768" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="769" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A769" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="770" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A770" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="771" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A771" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="772" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A772" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="773" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A773" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="774" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A774" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="775" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A775" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="776" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A776" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="777" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A777" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="778" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A778" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="779" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A779" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="780" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A780" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="781" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A781" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="782" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A782" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="783" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A783" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="784" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A784" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="785" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A785" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="786" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A786" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="787" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A787" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="788" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A788" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="789" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A789" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="790" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A790" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="791" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A791" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="792" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A792" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="793" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A793" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="794" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A794" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="795" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A795" t="s">
+        <v>794</v>
       </c>
     </row>
   </sheetData>
